--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Crow.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
